--- a/fix-errors/ig/FRDeviceUseLMCDAFHIR.xlsx
+++ b/fix-errors/ig/FRDeviceUseLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T08:13:43+00:00</t>
+    <t>2026-08-18T11:25:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -100,13 +100,13 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-device-use</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-device-use|0.1.0</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-cda-dispositif-medical</t>
+    <t>https://interop.esante.gouv.fr/ig/cda/document-core/StructureDefinition/fr-cda-dispositif-medical|0.1.0</t>
   </si>
   <si>
     <t>FRLMDeviceUse</t>
@@ -190,7 +190,7 @@
     <t>FRCDADispositifMedical.text</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-device-use-statement-document</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-device-use-statement-document|0.1.0</t>
   </si>
   <si>
     <t>FRDeviceUseStatementDocument</t>
